--- a/User_Test_Data_2024_25.xlsx
+++ b/User_Test_Data_2024_25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annalenaroth/Desktop/Dissertation/Python_Studies/Collective_Operations_Study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annalenaroth/Desktop/EduMPI_User_Study_24_25_Coll_Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48A272C-B9A5-2348-A340-025FE33B8E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D08655F-85D2-7A4B-BEA6-4D735A2D9E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WiSe2024_25" sheetId="1" r:id="rId1"/>
@@ -2280,20 +2280,6 @@
     <t>different algorithms, depending on array size</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">different algorithms (knomial, binary tree, basic linear), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>random decision</t>
-    </r>
-  </si>
-  <si>
     <t>different representations based on message size, number of processes, MPI library optimizations</t>
   </si>
   <si>
@@ -2318,20 +2304,6 @@
     <t>different algorithms (internally), depends on array size, MPI decides for the best option</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">different algorithms, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>EduMPI simulates</t>
-    </r>
-  </si>
-  <si>
     <t>adaptive broadcast strategies</t>
   </si>
   <si>
@@ -2375,13 +2347,19 @@
   </si>
   <si>
     <t>other</t>
+  </si>
+  <si>
+    <t>different algorithms, EduMPI simulates</t>
+  </si>
+  <si>
+    <t>different algorithms (knomial, binary tree, basic linear), random decision</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -2390,12 +2368,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2445,14 +2417,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2873,13 +2845,13 @@
         <v>158</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>165</v>
@@ -3010,19 +2982,19 @@
         <v>158</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>288</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>194</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>190</v>
@@ -3040,7 +3012,7 @@
         <v>195</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>196</v>
@@ -3061,7 +3033,7 @@
         <v>197</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>192</v>
@@ -3094,7 +3066,7 @@
         <v>203</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AP2" s="3" t="s">
         <v>204</v>
@@ -3120,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -3278,7 +3250,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>207</v>
@@ -3799,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E8" t="s">
         <v>2</v>
@@ -4621,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
@@ -4758,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -4787,10 +4759,10 @@
       <c r="M15" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="9" t="s">
         <v>207</v>
       </c>
       <c r="P15" s="4" t="s">
@@ -4892,7 +4864,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E16" t="s">
         <v>2</v>
@@ -4922,7 +4894,7 @@
         <v>209</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>209</v>
@@ -6141,7 +6113,7 @@
         <v>17</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>209</v>
@@ -6391,7 +6363,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E27" t="s">
         <v>2</v>
@@ -6968,10 +6940,10 @@
       <c r="M31" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="N31" s="5" t="s">
+      <c r="N31" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="9" t="s">
         <v>207</v>
       </c>
       <c r="P31" t="s">
@@ -7199,13 +7171,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="12:41" x14ac:dyDescent="0.2">
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="AO33">
-        <f>COUNTIF(AO3:AO32, "partly applies")</f>
-        <v>4</v>
-      </c>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -7215,159 +7183,159 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE87763-B9F5-744B-B272-C72F2B80BA8C}">
-  <dimension ref="A1:AT38"/>
+  <dimension ref="A1:AT37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="7"/>
-    <col min="2" max="2" width="37.5" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="7"/>
-    <col min="4" max="4" width="21" style="7" customWidth="1"/>
-    <col min="5" max="5" width="23" style="7" customWidth="1"/>
-    <col min="6" max="6" width="21.83203125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="39" style="7" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="26" style="7" customWidth="1"/>
-    <col min="11" max="12" width="13.5" style="7" customWidth="1"/>
-    <col min="13" max="13" width="46.1640625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="21" style="7" customWidth="1"/>
-    <col min="15" max="15" width="36.5" style="7" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" style="7" customWidth="1"/>
-    <col min="17" max="17" width="36.5" style="7" customWidth="1"/>
-    <col min="18" max="19" width="13.1640625" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" style="7" customWidth="1"/>
-    <col min="21" max="21" width="46.6640625" style="7" customWidth="1"/>
-    <col min="22" max="22" width="25.33203125" style="7" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" style="7" customWidth="1"/>
-    <col min="24" max="24" width="25.1640625" style="7" customWidth="1"/>
-    <col min="25" max="26" width="14.1640625" style="7" customWidth="1"/>
-    <col min="27" max="27" width="18.83203125" style="7" customWidth="1"/>
-    <col min="28" max="28" width="49.5" style="7" customWidth="1"/>
-    <col min="29" max="29" width="28" style="7" customWidth="1"/>
-    <col min="30" max="30" width="18.5" style="7" customWidth="1"/>
-    <col min="31" max="31" width="13.1640625" style="7" customWidth="1"/>
-    <col min="32" max="32" width="25.6640625" style="7" customWidth="1"/>
-    <col min="33" max="33" width="13.6640625" style="7" customWidth="1"/>
-    <col min="34" max="34" width="30.83203125" style="7" customWidth="1"/>
-    <col min="35" max="35" width="13.6640625" style="7" customWidth="1"/>
-    <col min="36" max="36" width="19.83203125" style="7" customWidth="1"/>
-    <col min="37" max="37" width="67.33203125" style="7" customWidth="1"/>
-    <col min="38" max="38" width="38.6640625" style="7" customWidth="1"/>
-    <col min="39" max="39" width="26.33203125" style="7" customWidth="1"/>
-    <col min="40" max="40" width="22.5" style="7" customWidth="1"/>
-    <col min="41" max="41" width="27.6640625" style="7" customWidth="1"/>
-    <col min="42" max="42" width="30" style="7" customWidth="1"/>
-    <col min="43" max="43" width="22.5" style="7" customWidth="1"/>
-    <col min="44" max="44" width="18.6640625" style="7" customWidth="1"/>
-    <col min="45" max="45" width="20.5" style="7" customWidth="1"/>
-    <col min="46" max="46" width="21.6640625" style="7" customWidth="1"/>
-    <col min="47" max="16384" width="10.83203125" style="7"/>
+    <col min="1" max="1" width="10.83203125" style="6"/>
+    <col min="2" max="2" width="37.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="6"/>
+    <col min="4" max="4" width="21" style="6" customWidth="1"/>
+    <col min="5" max="5" width="23" style="6" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="39" style="6" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="26" style="6" customWidth="1"/>
+    <col min="11" max="12" width="13.5" style="6" customWidth="1"/>
+    <col min="13" max="13" width="46.1640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21" style="6" customWidth="1"/>
+    <col min="15" max="15" width="36.5" style="6" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="36.5" style="6" customWidth="1"/>
+    <col min="18" max="19" width="13.1640625" style="6" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" style="6" customWidth="1"/>
+    <col min="21" max="21" width="46.6640625" style="6" customWidth="1"/>
+    <col min="22" max="22" width="25.33203125" style="6" customWidth="1"/>
+    <col min="23" max="23" width="20.33203125" style="6" customWidth="1"/>
+    <col min="24" max="24" width="25.1640625" style="6" customWidth="1"/>
+    <col min="25" max="26" width="14.1640625" style="6" customWidth="1"/>
+    <col min="27" max="27" width="18.83203125" style="6" customWidth="1"/>
+    <col min="28" max="28" width="49.5" style="6" customWidth="1"/>
+    <col min="29" max="29" width="28" style="6" customWidth="1"/>
+    <col min="30" max="30" width="18.5" style="6" customWidth="1"/>
+    <col min="31" max="31" width="13.1640625" style="6" customWidth="1"/>
+    <col min="32" max="32" width="25.6640625" style="6" customWidth="1"/>
+    <col min="33" max="33" width="13.6640625" style="6" customWidth="1"/>
+    <col min="34" max="34" width="30.83203125" style="6" customWidth="1"/>
+    <col min="35" max="35" width="13.6640625" style="6" customWidth="1"/>
+    <col min="36" max="36" width="19.83203125" style="6" customWidth="1"/>
+    <col min="37" max="37" width="67.33203125" style="6" customWidth="1"/>
+    <col min="38" max="38" width="38.6640625" style="6" customWidth="1"/>
+    <col min="39" max="39" width="26.33203125" style="6" customWidth="1"/>
+    <col min="40" max="40" width="22.5" style="6" customWidth="1"/>
+    <col min="41" max="41" width="27.6640625" style="6" customWidth="1"/>
+    <col min="42" max="42" width="30" style="6" customWidth="1"/>
+    <col min="43" max="43" width="22.5" style="6" customWidth="1"/>
+    <col min="44" max="44" width="18.6640625" style="6" customWidth="1"/>
+    <col min="45" max="45" width="20.5" style="6" customWidth="1"/>
+    <col min="46" max="46" width="21.6640625" style="6" customWidth="1"/>
+    <col min="47" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="M1" s="9" t="s">
+      <c r="L1" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="N1" s="9" t="s">
-        <v>761</v>
-      </c>
-      <c r="O1" s="9" t="s">
+      <c r="N1" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AE1" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AF1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AG1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AH1" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AI1" s="8" t="s">
         <v>175</v>
       </c>
       <c r="AJ1" s="1" t="s">
@@ -7376,138 +7344,138 @@
       <c r="AK1" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AL1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AM1" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AN1" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AO1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="AP1" s="9" t="s">
+      <c r="AP1" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="AQ1" s="9" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="AR1" s="9" t="s">
+      <c r="AR1" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AS1" s="9" t="s">
+      <c r="AS1" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AT1" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>189</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>760</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="V2" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="AC2" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AC2" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="AD2" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="AF2" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="7" t="s">
         <v>175</v>
       </c>
       <c r="AJ2" s="2" t="s">
@@ -7516,4914 +7484,4908 @@
       <c r="AK2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="AL2" s="8" t="s">
+      <c r="AL2" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AM2" s="8" t="s">
+      <c r="AM2" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="AN2" s="8" t="s">
-        <v>767</v>
-      </c>
-      <c r="AO2" s="8" t="s">
+      <c r="AN2" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="AO2" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="AP2" s="8" t="s">
+      <c r="AP2" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="AQ2" s="8" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="AR2" s="8" t="s">
+      <c r="AR2" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="AS2" s="8" t="s">
+      <c r="AS2" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AT2" s="8" t="s">
+      <c r="AT2" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="D3" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="H3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="K3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O3" s="7" t="s">
+      <c r="N3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="7" t="s">
+      <c r="P3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="R3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X3" s="7" t="s">
+      <c r="R3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X3" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="Y3" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB3" s="7" t="s">
+      <c r="Y3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AC3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="AE3" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AE3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF3" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="AG3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AG3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH3" s="6" t="s">
         <v>738</v>
       </c>
-      <c r="AI3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AI3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK3" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AL3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AM3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AP3" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="AQ3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AQ3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS3" s="6" t="s">
         <v>673</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AT3" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
-        <v>2</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>672</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="G4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M4" s="7" t="s">
+      <c r="K4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="7" t="s">
+      <c r="N4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="R4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X4" s="7" t="s">
+      <c r="R4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="Y4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA4" s="7" t="s">
+      <c r="Y4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA4" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD4" s="7" t="s">
+      <c r="AB4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="AE4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF4" s="7" t="s">
+      <c r="AE4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF4" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="AG4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH4" s="7" t="s">
+      <c r="AG4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH4" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="AI4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ4" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK4" s="7" t="s">
+      <c r="AI4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK4" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="AL4" s="7" t="s">
+      <c r="AL4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM4" s="7" t="s">
+      <c r="AM4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AN4" s="7" t="s">
+      <c r="AN4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AO4" s="7" t="s">
+      <c r="AO4" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="AP4" s="7" t="s">
+      <c r="AP4" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="AQ4" s="7" t="s">
+      <c r="AQ4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS4" s="7" t="s">
+      <c r="AR4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS4" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="AT4" s="7" t="s">
+      <c r="AT4" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>3</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>662</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="G5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M5" s="7" t="s">
+      <c r="K5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="7" t="s">
+      <c r="N5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="R5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T5" s="7" t="s">
+      <c r="R5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T5" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X5" s="7" t="s">
+      <c r="U5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X5" s="6" t="s">
         <v>708</v>
       </c>
-      <c r="Y5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="7" t="s">
+      <c r="Y5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD5" s="7" t="s">
+      <c r="AD5" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="AE5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF5" s="7" t="s">
+      <c r="AE5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF5" s="6" t="s">
         <v>658</v>
       </c>
-      <c r="AG5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH5" s="7" t="s">
+      <c r="AG5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH5" s="6" t="s">
         <v>657</v>
       </c>
-      <c r="AI5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ5" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO5" s="7" t="s">
+      <c r="AI5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="6" t="s">
         <v>656</v>
       </c>
-      <c r="AP5" s="7" t="s">
+      <c r="AP5" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="AQ5" s="7" t="s">
+      <c r="AQ5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS5" s="7" t="s">
+      <c r="AR5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS5" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="AT5" s="7" t="s">
+      <c r="AT5" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="G6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>652</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" s="7" t="s">
+      <c r="K6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="7" t="s">
+      <c r="O6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="6" t="s">
         <v>651</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X6" s="7" t="s">
+      <c r="R6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X6" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="Y6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA6" s="7" t="s">
+      <c r="Y6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA6" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB6" s="7" t="s">
+      <c r="AB6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC6" s="7" t="s">
+      <c r="AC6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD6" s="7" t="s">
+      <c r="AD6" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="AE6" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF6" s="7" t="s">
+      <c r="AE6" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF6" s="6" t="s">
         <v>649</v>
       </c>
-      <c r="AG6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH6" s="7" t="s">
+      <c r="AG6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH6" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="AI6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ6" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO6" s="7" t="s">
+      <c r="AI6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ6" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO6" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="AP6" s="7" t="s">
+      <c r="AP6" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="AQ6" s="7" t="s">
+      <c r="AQ6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS6" s="7" t="s">
+      <c r="AR6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS6" s="6" t="s">
         <v>645</v>
       </c>
-      <c r="AT6" s="7" t="s">
+      <c r="AT6" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="6">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>644</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="G7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M7" s="7" t="s">
+      <c r="K7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="7" t="s">
+      <c r="N7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T7" s="7" t="s">
+      <c r="R7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T7" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X7" s="7" t="s">
+      <c r="U7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X7" s="6" t="s">
         <v>642</v>
       </c>
-      <c r="Y7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="7" t="s">
+      <c r="Y7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD7" s="7" t="s">
+      <c r="AD7" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="AE7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF7" s="7" t="s">
+      <c r="AE7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF7" s="6" t="s">
         <v>640</v>
       </c>
-      <c r="AG7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH7" s="7" t="s">
+      <c r="AG7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH7" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="AI7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ7" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK7" s="7" t="s">
+      <c r="AI7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK7" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="AL7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO7" s="7" t="s">
+      <c r="AL7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="AP7" s="7" t="s">
+      <c r="AP7" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="AQ7" s="7" t="s">
+      <c r="AQ7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS7" s="7" t="s">
+      <c r="AR7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS7" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="AT7" s="7" t="s">
+      <c r="AT7" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="G8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M8" s="7" t="s">
+      <c r="K8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="7" t="s">
+      <c r="O8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="R8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X8" s="7" t="s">
+      <c r="R8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X8" s="6" t="s">
         <v>710</v>
       </c>
-      <c r="Y8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="7" t="s">
+      <c r="Y8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD8" s="7" t="s">
+      <c r="AD8" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="AE8" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF8" s="7" t="s">
+      <c r="AE8" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF8" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="AG8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH8" s="7" t="s">
+      <c r="AG8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH8" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="AI8" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK8" s="7" t="s">
+      <c r="AI8" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK8" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="AL8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO8" s="7" t="s">
+      <c r="AL8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="AP8" s="7" t="s">
+      <c r="AP8" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="AQ8" s="7" t="s">
+      <c r="AQ8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS8" s="7" t="s">
+      <c r="AR8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS8" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="AT8" s="7" t="s">
+      <c r="AT8" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="G9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M9" s="7" t="s">
+      <c r="J9" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="7" t="s">
+      <c r="O9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="R9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="7" t="s">
+      <c r="R9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="Y9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC9" s="7" t="s">
+      <c r="Y9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD9" s="7" t="s">
+      <c r="AD9" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="AE9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF9" s="7" t="s">
+      <c r="AE9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF9" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="AG9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH9" s="7" t="s">
+      <c r="AG9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH9" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="AI9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ9" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK9" s="7" t="s">
+      <c r="AI9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK9" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="AL9" s="7" t="s">
+      <c r="AL9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO9" s="7" t="s">
+      <c r="AM9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="AP9" s="7" t="s">
+      <c r="AP9" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="AQ9" s="7" t="s">
+      <c r="AQ9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS9" s="7" t="s">
+      <c r="AR9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS9" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="AT9" s="7" t="s">
+      <c r="AT9" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7">
-        <v>5</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="6">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="K10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>688</v>
       </c>
-      <c r="N10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O10" s="7" t="s">
+      <c r="N10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="7" t="s">
+      <c r="P10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="R10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U10" s="7" t="s">
+      <c r="R10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="V10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="7" t="s">
+      <c r="V10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="Y10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA10" s="7" t="s">
+      <c r="Y10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA10" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB10" s="7" t="s">
+      <c r="AB10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC10" s="7" t="s">
+      <c r="AC10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD10" s="7" t="s">
+      <c r="AD10" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="AE10" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF10" s="7" t="s">
+      <c r="AE10" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF10" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="AG10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH10" s="7" t="s">
+      <c r="AG10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH10" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="AI10" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK10" s="7" t="s">
+      <c r="AI10" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK10" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="AL10" s="7" t="s">
+      <c r="AL10" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="AM10" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO10" s="7" t="s">
+      <c r="AM10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="AP10" s="7" t="s">
+      <c r="AP10" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="AQ10" s="7" t="s">
+      <c r="AQ10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS10" s="7" t="s">
+      <c r="AR10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS10" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="AT10" s="7" t="s">
+      <c r="AT10" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="D11" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M11" s="7" t="s">
+      <c r="K11" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="N11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="7" t="s">
+      <c r="N11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="R11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X11" s="7" t="s">
+      <c r="R11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X11" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="Y11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB11" s="7" t="s">
+      <c r="Y11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB11" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="AC11" s="7" t="s">
+      <c r="AC11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD11" s="7" t="s">
+      <c r="AD11" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="AE11" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF11" s="7" t="s">
+      <c r="AE11" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF11" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="AG11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH11" s="7" t="s">
+      <c r="AG11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH11" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="AI11" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK11" s="7" t="s">
+      <c r="AI11" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK11" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="AL11" s="7" t="s">
+      <c r="AL11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AM11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO11" s="7" t="s">
+      <c r="AM11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO11" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="AP11" s="7" t="s">
+      <c r="AP11" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="AQ11" s="7" t="s">
+      <c r="AQ11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS11" s="7" t="s">
+      <c r="AR11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS11" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="AT11" s="7" t="s">
+      <c r="AT11" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>6</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="G12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M12" s="7" t="s">
+      <c r="K12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="7" t="s">
+      <c r="P12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="R12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T12" s="7" t="s">
+      <c r="R12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T12" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X12" s="7" t="s">
+      <c r="U12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X12" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="Y12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB12" s="7" t="s">
+      <c r="Y12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC12" s="7" t="s">
+      <c r="AC12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD12" s="7" t="s">
+      <c r="AD12" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="AE12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF12" s="7" t="s">
+      <c r="AE12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF12" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="AG12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH12" s="7" t="s">
+      <c r="AG12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH12" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="AI12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK12" s="7" t="s">
+      <c r="AI12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK12" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="AL12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO12" s="7" t="s">
+      <c r="AL12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="AP12" s="7" t="s">
+      <c r="AP12" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="AQ12" s="7" t="s">
+      <c r="AQ12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS12" s="7" t="s">
+      <c r="AR12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS12" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="AT12" s="7" t="s">
+      <c r="AT12" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>6</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="G13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="7" t="s">
+      <c r="K13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="R13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T13" s="7" t="s">
+      <c r="R13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T13" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X13" s="7" t="s">
+      <c r="U13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X13" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="Y13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC13" s="7" t="s">
+      <c r="Y13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD13" s="7" t="s">
+      <c r="AD13" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="AE13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF13" s="7" t="s">
+      <c r="AE13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF13" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="AG13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH13" s="7" t="s">
+      <c r="AG13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH13" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="AI13" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK13" s="7" t="s">
+      <c r="AI13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK13" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="AL13" s="7" t="s">
+      <c r="AL13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AM13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO13" s="7" t="s">
+      <c r="AM13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO13" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="AP13" s="7" t="s">
+      <c r="AP13" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="AQ13" s="7" t="s">
+      <c r="AQ13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS13" s="7" t="s">
+      <c r="AR13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS13" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="AT13" s="7" t="s">
+      <c r="AT13" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>1</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="D14" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="H14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M14" s="7" t="s">
+      <c r="K14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="N14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O14" s="7" t="s">
+      <c r="N14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="7" t="s">
+      <c r="P14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="R14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U14" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="7" t="s">
+      <c r="R14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="Y14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB14" s="7" t="s">
+      <c r="Y14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="7" t="s">
+      <c r="AC14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="AE14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF14" s="7" t="s">
+      <c r="AE14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF14" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="AG14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH14" s="7" t="s">
+      <c r="AG14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH14" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="AI14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK14" s="7" t="s">
+      <c r="AI14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK14" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="AL14" s="7" t="s">
+      <c r="AL14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AM14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO14" s="7" t="s">
+      <c r="AM14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO14" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="AP14" s="7" t="s">
+      <c r="AP14" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="AQ14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS14" s="7" t="s">
+      <c r="AQ14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS14" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="AT14" s="7" t="s">
+      <c r="AT14" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="7">
-        <v>4</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="6">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="7" t="s">
+      <c r="H15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M15" s="7" t="s">
+      <c r="K15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="P15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="7" t="s">
+      <c r="P15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U15" s="7" t="s">
+      <c r="R15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X15" s="7" t="s">
+      <c r="V15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X15" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="Y15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB15" s="7" t="s">
+      <c r="Y15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD15" s="7" t="s">
+      <c r="AC15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD15" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="AE15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF15" s="7" t="s">
+      <c r="AE15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF15" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="AG15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH15" s="7" t="s">
+      <c r="AG15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH15" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="AI15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ15" s="7" t="s">
+      <c r="AI15" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ15" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK15" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="AL15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO15" s="7" t="s">
+      <c r="AK15" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="AL15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO15" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="AP15" s="7" t="s">
+      <c r="AP15" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="AQ15" s="7" t="s">
+      <c r="AQ15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS15" s="7" t="s">
+      <c r="AR15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS15" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="AT15" s="7" t="s">
+      <c r="AT15" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="7">
-        <v>2</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="C16" s="6">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="G16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>694</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M16" s="7" t="s">
+      <c r="K16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="N16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O16" s="7" t="s">
+      <c r="N16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="7" t="s">
+      <c r="P16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="R16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X16" s="7" t="s">
+      <c r="R16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X16" s="6" t="s">
         <v>730</v>
       </c>
-      <c r="Y16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC16" s="7" t="s">
+      <c r="Y16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD16" s="7" t="s">
+      <c r="AD16" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="AE16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF16" s="7" t="s">
+      <c r="AE16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF16" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="AG16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH16" s="7" t="s">
+      <c r="AG16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH16" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="AI16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK16" s="7" t="s">
+      <c r="AI16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK16" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="AL16" s="7" t="s">
+      <c r="AL16" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="AM16" s="7" t="s">
+      <c r="AM16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO16" s="7" t="s">
+      <c r="AN16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO16" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="AP16" s="7" t="s">
+      <c r="AP16" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="AQ16" s="7" t="s">
+      <c r="AQ16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS16" s="7" t="s">
+      <c r="AR16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS16" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="AT16" s="7" t="s">
+      <c r="AT16" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>3</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="E17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="G17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M17" s="7" t="s">
+      <c r="K17" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M17" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="N17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="7" t="s">
+      <c r="N17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="R17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="7" t="s">
+      <c r="R17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T17" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="6" t="s">
         <v>731</v>
       </c>
-      <c r="Y17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA17" s="7" t="s">
+      <c r="Y17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA17" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC17" s="7" t="s">
+      <c r="AB17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD17" s="7" t="s">
+      <c r="AD17" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="AE17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF17" s="7" t="s">
+      <c r="AE17" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF17" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="AG17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH17" s="7" t="s">
+      <c r="AG17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH17" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="AI17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK17" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="AL17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO17" s="7" t="s">
+      <c r="AI17" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK17" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="AL17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO17" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="AP17" s="7" t="s">
+      <c r="AP17" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="AQ17" s="7" t="s">
+      <c r="AQ17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS17" s="7" t="s">
+      <c r="AR17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS17" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="AT17" s="7" t="s">
+      <c r="AT17" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="G18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M18" s="7" t="s">
+      <c r="K18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="N18" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O18" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q18" s="7" t="s">
+      <c r="O18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="R18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T18" s="7" t="s">
+      <c r="R18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T18" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="7" t="s">
+      <c r="U18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="6" t="s">
         <v>716</v>
       </c>
-      <c r="Y18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB18" s="7" t="s">
+      <c r="Y18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC18" s="7" t="s">
+      <c r="AC18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD18" s="7" t="s">
+      <c r="AD18" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="AE18" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF18" s="7" t="s">
+      <c r="AE18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF18" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="AG18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH18" s="7" t="s">
+      <c r="AG18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH18" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="AI18" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK18" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="AL18" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO18" s="7" t="s">
+      <c r="AI18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK18" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="AL18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO18" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="AP18" s="7" t="s">
+      <c r="AP18" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="AQ18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS18" s="7" t="s">
+      <c r="AQ18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS18" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="AT18" s="7" t="s">
+      <c r="AT18" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>1</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="G19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M19" s="7" t="s">
+      <c r="K19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>698</v>
       </c>
-      <c r="N19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q19" s="7" t="s">
+      <c r="N19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q19" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="R19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X19" s="7" t="s">
+      <c r="R19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X19" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="Y19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC19" s="7" t="s">
+      <c r="Y19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD19" s="7" t="s">
+      <c r="AD19" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="AE19" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF19" s="7" t="s">
+      <c r="AE19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF19" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="AG19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH19" s="7" t="s">
+      <c r="AG19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH19" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="AI19" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK19" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="AL19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM19" s="7" t="s">
+      <c r="AI19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ19" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK19" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="AL19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AN19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO19" s="7" t="s">
+      <c r="AN19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO19" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="AP19" s="7" t="s">
+      <c r="AP19" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="AQ19" s="7" t="s">
+      <c r="AQ19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS19" s="7" t="s">
+      <c r="AR19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS19" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="AT19" s="7" t="s">
+      <c r="AT19" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>1</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="7" t="s">
+      <c r="G20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M20" s="7" t="s">
+      <c r="K20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="N20" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q20" s="7" t="s">
+      <c r="O20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q20" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="R20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X20" s="7" t="s">
+      <c r="R20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X20" s="6" t="s">
         <v>729</v>
       </c>
-      <c r="Y20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB20" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="7" t="s">
+      <c r="Y20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD20" s="7" t="s">
+      <c r="AD20" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="AE20" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF20" s="7" t="s">
+      <c r="AE20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF20" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="AG20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH20" s="7" t="s">
+      <c r="AG20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH20" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="AI20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ20" s="7" t="s">
+      <c r="AI20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ20" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK20" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="AL20" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM20" s="7" t="s">
+      <c r="AK20" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="AL20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO20" s="7" t="s">
+      <c r="AN20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO20" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="AP20" s="7" t="s">
+      <c r="AP20" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="AQ20" s="7" t="s">
+      <c r="AQ20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS20" s="7" t="s">
+      <c r="AR20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS20" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="AT20" s="7" t="s">
+      <c r="AT20" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>1</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="E21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="7" t="s">
+      <c r="G21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M21" s="7" t="s">
+      <c r="K21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M21" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="N21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q21" s="7" t="s">
+      <c r="N21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="R21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X21" s="7" t="s">
+      <c r="R21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X21" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="Y21" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB21" s="7" t="s">
+      <c r="Y21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC21" s="7" t="s">
+      <c r="AC21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD21" s="7" t="s">
+      <c r="AD21" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="AE21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF21" s="7" t="s">
+      <c r="AE21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF21" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="AG21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH21" s="7" t="s">
+      <c r="AG21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH21" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="AI21" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK21" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="AL21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="7" t="s">
+      <c r="AI21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK21" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="AL21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO21" s="7" t="s">
+      <c r="AN21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO21" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="AP21" s="7" t="s">
+      <c r="AP21" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="AQ21" s="7" t="s">
+      <c r="AQ21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS21" s="7" t="s">
+      <c r="AR21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS21" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="AT21" s="7" t="s">
+      <c r="AT21" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="E22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="7" t="s">
+      <c r="H22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="6" t="s">
         <v>702</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M22" s="7" t="s">
+      <c r="K22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="N22" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="O22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="P22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q22" s="7" t="s">
+      <c r="P22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="R22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="7" t="s">
+      <c r="R22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="Y22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD22" s="7" t="s">
+      <c r="Y22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="AE22" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF22" s="7" t="s">
+      <c r="AE22" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF22" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="AG22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH22" s="7" t="s">
+      <c r="AG22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH22" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="AI22" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ22" s="7" t="s">
+      <c r="AI22" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ22" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK22" s="7" t="s">
+      <c r="AK22" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="AL22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO22" s="7" t="s">
+      <c r="AL22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO22" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="AP22" s="7" t="s">
+      <c r="AP22" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="AQ22" s="7" t="s">
+      <c r="AQ22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS22" s="7" t="s">
+      <c r="AR22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS22" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="AT22" s="7" t="s">
+      <c r="AT22" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="7">
-        <v>2</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="C23" s="6">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="7" t="s">
+      <c r="G23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="K23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M23" s="7" t="s">
+      <c r="K23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="N23" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q23" s="7" t="s">
+      <c r="O23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q23" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="R23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T23" s="7" t="s">
+      <c r="R23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T23" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X23" s="7" t="s">
+      <c r="U23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X23" s="6" t="s">
         <v>719</v>
       </c>
-      <c r="Y23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC23" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="7" t="s">
+      <c r="Y23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="AE23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF23" s="7" t="s">
+      <c r="AE23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF23" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="AG23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH23" s="7" t="s">
+      <c r="AG23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH23" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="AI23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK23" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="AL23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM23" s="7" t="s">
+      <c r="AI23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK23" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="AL23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO23" s="7" t="s">
+      <c r="AN23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO23" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="AP23" s="7" t="s">
+      <c r="AP23" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="AQ23" s="7" t="s">
+      <c r="AQ23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR23" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS23" s="7" t="s">
+      <c r="AR23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS23" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="AT23" s="7" t="s">
+      <c r="AT23" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="7" t="s">
+      <c r="G24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M24" s="7" t="s">
+      <c r="K24" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="N24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q24" s="7" t="s">
+      <c r="N24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="R24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U24" s="7" t="s">
+      <c r="R24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X24" s="7" t="s">
+      <c r="V24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X24" s="6" t="s">
         <v>736</v>
       </c>
-      <c r="Y24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC24" s="7" t="s">
+      <c r="Y24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD24" s="7" t="s">
+      <c r="AD24" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="AE24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF24" s="7" t="s">
+      <c r="AE24" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF24" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="AG24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH24" s="7" t="s">
+      <c r="AG24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH24" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="AI24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK24" s="7" t="s">
+      <c r="AI24" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ24" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK24" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="AL24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO24" s="7" t="s">
+      <c r="AL24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO24" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="AP24" s="7" t="s">
+      <c r="AP24" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="AQ24" s="7" t="s">
+      <c r="AQ24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR24" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS24" s="7" t="s">
+      <c r="AR24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS24" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="AT24" s="7" t="s">
+      <c r="AT24" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>1</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I25" s="7" t="s">
+      <c r="H25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M25" s="7" t="s">
+      <c r="K25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M25" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="N25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O25" s="7" t="s">
+      <c r="N25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="P25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q25" s="7" t="s">
+      <c r="P25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="R25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X25" s="7" t="s">
+      <c r="R25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X25" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="Y25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB25" s="7" t="s">
+      <c r="Y25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD25" s="7" t="s">
+      <c r="AC25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD25" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="AE25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF25" s="7" t="s">
+      <c r="AE25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF25" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="AG25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH25" s="7" t="s">
+      <c r="AG25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH25" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="AI25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ25" s="7" t="s">
+      <c r="AI25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ25" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK25" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="AL25" s="7" t="s">
+      <c r="AK25" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="AL25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AM25" s="7" t="s">
+      <c r="AM25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO25" s="7" t="s">
+      <c r="AN25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO25" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="AP25" s="7" t="s">
+      <c r="AP25" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="AQ25" s="7" t="s">
+      <c r="AQ25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS25" s="7" t="s">
+      <c r="AR25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS25" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="AT25" s="7" t="s">
+      <c r="AT25" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>1</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="G26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="K26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M26" s="7" t="s">
+      <c r="K26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="N26" s="7" t="s">
+      <c r="N26" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q26" s="7" t="s">
+      <c r="O26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q26" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="R26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X26" s="7" t="s">
+      <c r="R26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X26" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="Y26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA26" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC26" s="7" t="s">
+      <c r="Y26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD26" s="7" t="s">
+      <c r="AD26" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="AE26" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF26" s="7" t="s">
+      <c r="AE26" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF26" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="AG26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH26" s="7" t="s">
+      <c r="AG26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH26" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="AI26" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK26" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="AL26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO26" s="7" t="s">
+      <c r="AI26" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ26" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK26" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="AL26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO26" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="AP26" s="7" t="s">
+      <c r="AP26" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="AQ26" s="7" t="s">
+      <c r="AQ26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS26" s="7" t="s">
+      <c r="AR26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS26" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="AT26" s="7" t="s">
+      <c r="AT26" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="7">
-        <v>2</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="E27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="7" t="s">
+      <c r="G27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M27" s="7" t="s">
+      <c r="K27" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M27" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="N27" s="7" t="s">
+      <c r="N27" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="7" t="s">
+      <c r="O27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="R27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X27" s="7" t="s">
+      <c r="R27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X27" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="Y27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="7" t="s">
+      <c r="Y27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="AE27" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF27" s="7" t="s">
+      <c r="AE27" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF27" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="AG27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH27" s="7" t="s">
+      <c r="AG27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH27" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="AI27" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK27" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="AL27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM27" s="7" t="s">
+      <c r="AI27" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK27" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="AL27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO27" s="7" t="s">
+      <c r="AN27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO27" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="AP27" s="7" t="s">
+      <c r="AP27" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="AQ27" s="7" t="s">
+      <c r="AQ27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS27" s="7" t="s">
+      <c r="AR27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS27" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="AT27" s="7" t="s">
+      <c r="AT27" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>1</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="7" t="s">
+      <c r="G28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M28" s="7" t="s">
+      <c r="K28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="N28" s="7" t="s">
+      <c r="N28" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O28" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q28" s="7" t="s">
+      <c r="O28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="R28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T28" s="7" t="s">
+      <c r="R28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T28" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U28" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X28" s="7" t="s">
+      <c r="U28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X28" s="6" t="s">
         <v>721</v>
       </c>
-      <c r="Y28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA28" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB28" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC28" s="7" t="s">
+      <c r="Y28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA28" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD28" s="7" t="s">
+      <c r="AD28" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="AE28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF28" s="7" t="s">
+      <c r="AE28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF28" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="AG28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH28" s="7" t="s">
+      <c r="AG28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH28" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="AI28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ28" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL28" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM28" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO28" s="7" t="s">
+      <c r="AI28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ28" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO28" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="AP28" s="7" t="s">
+      <c r="AP28" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="AQ28" s="7" t="s">
+      <c r="AQ28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS28" s="7" t="s">
+      <c r="AR28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS28" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="AT28" s="7" t="s">
+      <c r="AT28" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>1</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="7" t="s">
+      <c r="G29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M29" s="7" t="s">
+      <c r="K29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q29" s="7" t="s">
+      <c r="O29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q29" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="R29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="7" t="s">
+      <c r="R29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="Y29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA29" s="7" t="s">
+      <c r="Y29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA29" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC29" s="7" t="s">
+      <c r="AB29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD29" s="7" t="s">
+      <c r="AD29" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="AE29" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF29" s="7" t="s">
+      <c r="AE29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF29" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="AG29" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH29" s="7" t="s">
+      <c r="AG29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH29" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="AI29" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ29" s="7" t="s">
+      <c r="AI29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ29" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK29" s="7" t="s">
+      <c r="AK29" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="AL29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO29" s="7" t="s">
+      <c r="AL29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO29" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="AP29" s="7" t="s">
+      <c r="AP29" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="AQ29" s="7" t="s">
+      <c r="AQ29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS29" s="7" t="s">
+      <c r="AR29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS29" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="AT29" s="7" t="s">
+      <c r="AT29" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="7">
-        <v>2</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I30" s="7" t="s">
+      <c r="G30" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M30" s="7" t="s">
+      <c r="K30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="N30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O30" s="7" t="s">
+      <c r="N30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q30" s="7" t="s">
+      <c r="P30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q30" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="R30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U30" s="7" t="s">
+      <c r="R30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X30" s="7" t="s">
+      <c r="V30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X30" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="Y30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC30" s="7" t="s">
+      <c r="Y30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB30" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD30" s="7" t="s">
+      <c r="AD30" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="AE30" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF30" s="7" t="s">
+      <c r="AE30" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF30" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="AG30" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH30" s="7" t="s">
+      <c r="AG30" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH30" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="AI30" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ30" s="7" t="s">
+      <c r="AI30" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ30" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK30" s="7" t="s">
+      <c r="AK30" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="AL30" s="7" t="s">
+      <c r="AL30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO30" s="7" t="s">
+      <c r="AM30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO30" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="AP30" s="7" t="s">
+      <c r="AP30" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="AQ30" s="7" t="s">
+      <c r="AQ30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS30" s="7" t="s">
+      <c r="AR30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS30" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="AT30" s="7" t="s">
+      <c r="AT30" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="7">
-        <v>4</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="6">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="G31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M31" s="7" t="s">
+      <c r="K31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="N31" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="7" t="s">
+      <c r="O31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="R31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X31" s="7" t="s">
+      <c r="R31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="W31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X31" s="6" t="s">
         <v>723</v>
       </c>
-      <c r="Y31" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB31" s="7" t="s">
+      <c r="Y31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC31" s="7" t="s">
+      <c r="AC31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD31" s="7" t="s">
+      <c r="AD31" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="AE31" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF31" s="7" t="s">
+      <c r="AE31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF31" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="AG31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH31" s="7" t="s">
+      <c r="AG31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH31" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="AI31" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ31" s="7" t="s">
+      <c r="AI31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ31" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK31" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="AL31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO31" s="7" t="s">
+      <c r="AK31" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="AL31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO31" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="AP31" s="7" t="s">
+      <c r="AP31" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="AQ31" s="7" t="s">
+      <c r="AQ31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS31" s="7" t="s">
+      <c r="AR31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS31" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="AT31" s="7" t="s">
+      <c r="AT31" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="7">
-        <v>2</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="7" t="s">
+      <c r="G32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M32" s="7" t="s">
+      <c r="K32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="N32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="7" t="s">
+      <c r="N32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="R32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U32" s="7" t="s">
+      <c r="R32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X32" s="7" t="s">
+      <c r="V32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X32" s="6" t="s">
         <v>733</v>
       </c>
-      <c r="Y32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB32" s="7" t="s">
+      <c r="Y32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC32" s="7" t="s">
+      <c r="AC32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD32" s="7" t="s">
+      <c r="AD32" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="AE32" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF32" s="7" t="s">
+      <c r="AE32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF32" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="AG32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH32" s="7" t="s">
+      <c r="AG32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH32" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="AI32" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ32" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL32" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM32" s="7" t="s">
+      <c r="AI32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO32" s="7" t="s">
+      <c r="AN32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO32" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="AP32" s="7" t="s">
+      <c r="AP32" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="AQ32" s="7" t="s">
+      <c r="AQ32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS32" s="7" t="s">
+      <c r="AR32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS32" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="AT32" s="7" t="s">
+      <c r="AT32" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="6">
         <v>1</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="7" t="s">
+      <c r="G33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M33" s="7" t="s">
+      <c r="K33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="N33" s="7" t="s">
+      <c r="N33" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O33" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="7" t="s">
+      <c r="O33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="R33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="U33" s="7" t="s">
+      <c r="R33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="V33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W33" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="7" t="s">
+      <c r="V33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="6" t="s">
         <v>724</v>
       </c>
-      <c r="Y33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA33" s="7" t="s">
+      <c r="Y33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA33" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AB33" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC33" s="7" t="s">
+      <c r="AB33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC33" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD33" s="7" t="s">
+      <c r="AD33" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="AE33" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF33" s="7" t="s">
+      <c r="AE33" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF33" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="AG33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH33" s="7" t="s">
+      <c r="AG33" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH33" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="AI33" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ33" s="7" t="s">
+      <c r="AI33" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ33" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK33" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="AL33" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM33" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO33" s="7" t="s">
+      <c r="AK33" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="AL33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO33" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="AP33" s="7" t="s">
+      <c r="AP33" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="AQ33" s="7" t="s">
+      <c r="AQ33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS33" s="7" t="s">
+      <c r="AR33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS33" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="AT33" s="7" t="s">
+      <c r="AT33" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>1</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="E34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I34" s="7" t="s">
+      <c r="H34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="7" t="s">
+      <c r="K34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="R34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="U34" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X34" s="7" t="s">
+      <c r="R34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X34" s="6" t="s">
         <v>725</v>
       </c>
-      <c r="Y34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB34" s="7" t="s">
+      <c r="Y34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB34" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AC34" s="7" t="s">
+      <c r="AC34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AD34" s="7" t="s">
+      <c r="AD34" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="AE34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF34" s="7" t="s">
+      <c r="AE34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF34" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="AG34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH34" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="AI34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ34" s="7" t="s">
+      <c r="AG34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH34" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="AI34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ34" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AK34" s="7" t="s">
+      <c r="AK34" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="AL34" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM34" s="7" t="s">
+      <c r="AL34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AN34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO34" s="7" t="s">
+      <c r="AN34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO34" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="AP34" s="7" t="s">
+      <c r="AP34" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="AQ34" s="7" t="s">
+      <c r="AQ34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS34" s="7" t="s">
+      <c r="AR34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS34" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="AT34" s="7" t="s">
+      <c r="AT34" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>1</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="E35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="7" t="s">
+      <c r="G35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M35" s="7" t="s">
+      <c r="K35" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M35" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="N35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q35" s="7" t="s">
+      <c r="N35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q35" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="R35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T35" s="7" t="s">
+      <c r="R35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T35" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U35" s="7" t="s">
+      <c r="U35" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="V35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X35" s="7" t="s">
+      <c r="V35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X35" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="Y35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB35" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC35" s="7" t="s">
+      <c r="Y35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC35" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD35" s="7" t="s">
+      <c r="AD35" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="AE35" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF35" s="7" t="s">
+      <c r="AE35" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF35" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="AG35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH35" s="7" t="s">
+      <c r="AG35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH35" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="AI35" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ35" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL35" s="7" t="s">
+      <c r="AI35" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ35" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO35" s="7" t="s">
+      <c r="AM35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO35" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="AP35" s="7" t="s">
+      <c r="AP35" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="AQ35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS35" s="7" t="s">
+      <c r="AQ35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS35" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="AT35" s="7" t="s">
+      <c r="AT35" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>1</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I36" s="7" t="s">
+      <c r="G36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M36" s="7" t="s">
+      <c r="K36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="N36" s="7" t="s">
+      <c r="N36" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O36" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P36" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q36" s="7" t="s">
+      <c r="O36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="R36" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="S36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T36" s="7" t="s">
+      <c r="R36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T36" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U36" s="7" t="s">
+      <c r="U36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="V36" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X36" s="7" t="s">
+      <c r="V36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X36" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="Y36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA36" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB36" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC36" s="7" t="s">
+      <c r="Y36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD36" s="7" t="s">
+      <c r="AD36" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="AE36" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF36" s="7" t="s">
+      <c r="AE36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF36" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="AG36" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH36" s="7" t="s">
+      <c r="AG36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH36" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="AI36" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ36" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL36" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM36" s="7" t="s">
+      <c r="AI36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO36" s="7" t="s">
+      <c r="AN36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO36" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="AP36" s="7" t="s">
+      <c r="AP36" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="AQ36" s="7" t="s">
+      <c r="AQ36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AR36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS36" s="7" t="s">
+      <c r="AR36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS36" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="AT36" s="7" t="s">
+      <c r="AT36" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>1</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="7" t="s">
+      <c r="G37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M37" s="7" t="s">
+      <c r="K37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M37" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="N37" s="7" t="s">
+      <c r="N37" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="O37" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q37" s="7" t="s">
+      <c r="O37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="R37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="T37" s="7" t="s">
+      <c r="R37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="T37" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U37" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="V37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="X37" s="7" t="s">
+      <c r="U37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X37" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="Y37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB37" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC37" s="7" t="s">
+      <c r="Y37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA37" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD37" s="7" t="s">
+      <c r="AD37" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="AE37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF37" s="7" t="s">
+      <c r="AE37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF37" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="AG37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH37" s="7" t="s">
+      <c r="AG37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH37" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="AI37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ37" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK37" s="7" t="s">
+      <c r="AI37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK37" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="AL37" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM37" s="7" t="s">
+      <c r="AL37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AN37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO37" s="7" t="s">
+      <c r="AN37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO37" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="AP37" s="7" t="s">
+      <c r="AP37" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="AQ37" s="7" t="s">
+      <c r="AQ37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AR37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS37" s="7" t="s">
+      <c r="AR37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS37" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="AT37" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="Y38" s="7">
-        <f>COUNTIF(Y3:Y37, "yes")</f>
-        <v>27</v>
+      <c r="AT37" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
